--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,87 +447,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>all elements (name | isPartOf)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.7931</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.8827</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>mean semantic meaning</t>
-        </is>
+      <c r="B3" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8874</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.8929</v>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mean semantic meaning</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4643</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3924</v>
+        <v>0.8846000000000001</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pageNumber</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>isPartOf</t>
+          <t>pageNumber</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.913</v>
+        <v>0.8462</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -538,15 +541,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>isPartOf</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9524</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>fixes</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -608,16 +626,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7143</v>
+        <v>0.8636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7407</v>
+        <v>0.7037</v>
       </c>
     </row>
     <row r="3">
@@ -652,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.3077</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7143</v>
+        <v>0.5714</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -717,56 +735,66 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>False Positives</t>
+          <t>Validated correct (name for units/patterns, isPartOf for connectors)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>False Negatives</t>
+          <t>False Positives</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Element Precision</t>
+          <t>False Negatives</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6512</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Element Recall</t>
+          <t>Precision (all elements; units/patterns by name, connectors by isPartOf)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7368</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Recall (all elements; units/patterns by name, connectors by isPartOf)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6842</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Match threshold (cosine)</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -836,22 +864,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -864,22 +892,22 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -892,22 +920,22 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +948,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -948,22 +976,22 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="n">
         <v>26</v>
-      </c>
-      <c r="E6" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" t="n">
-        <v>23</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21</v>
-      </c>
-      <c r="H6" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -991,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,12 +1141,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1127,11 +1155,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6125</v>
+        <v>0.6069</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Cloud Services Set</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1141,29 +1169,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Central service responsible for business logic and database interaction.</t>
+          <t>Collection of AWS services forming a data lake for historical data processing.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>AWS cloud services suite</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1173,21 +1201,21 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>The services used have different main functions that together allow the creation of the necessary infrastructure to manage the data on the platform. The main functions are the following: storage, data reading and data transmission.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1195,12 +1223,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1209,43 +1237,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7038</v>
+        <v>0.6682</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Web Platform</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Web interface of the Waapiti platform.</t>
+          <t>Main business logic service of the platform.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1255,21 +1283,21 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1277,12 +1305,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1291,43 +1319,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7198</v>
+        <v>0.6757</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cloud Services</t>
+          <t>Web Platform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collection of AWS services forming a data lake for historical data processing.</t>
+          <t>Web interface for the Waapiti platform.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>AWS cloud services suite</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1337,21 +1365,21 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>The services used have different main functions that together allow the creation of the necessary infrastructure to manage the data on the platform. The main functions are the following: storage, data reading and data transmission.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1359,12 +1387,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1373,43 +1401,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7537</v>
+        <v>0.7319</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Mobile Platform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Service responsible for management, authentication, authorization, and routing of API requests.</t>
+          <t>Mobile interface for the Waapiti platform.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>API Gateway Service</t>
+          <t>Waapiti Mobile Platform</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1419,21 +1447,21 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1441,12 +1469,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1455,43 +1483,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7567</v>
+        <v>0.7946</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mobile Platform</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mobile interface of the Waapiti platform.</t>
+          <t>Service responsible for management, authentication, authorization, and routing requests between clients and microservices.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1501,21 +1529,21 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1523,12 +1551,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1537,11 +1565,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7655</v>
+        <v>0.8002</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Analytics Module</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1551,39 +1579,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Service responsible for obtaining and processing playlogs, connections, and platform actions.</t>
+          <t>Relational database for storing system data.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>43, 62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>SQL database</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1591,13 +1619,13 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1619,7 +1647,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8178</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1643,7 +1671,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1687,81 +1715,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8312</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Relational database for storing system data.</t>
+          <t>The system is divided into three layers: presentation layer, business layer, and data layer.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1769,12 +1797,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1787,63 +1815,55 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A design pattern that allows only one component to interact between users and the services provided by the platform, handling authorization and SSL.</t>
+          <t>The platform is a web service where the client makes requests to a server that processes them and returns the response.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>['P_03']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>CF_M01_AD03</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1851,17 +1871,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1869,55 +1889,55 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The platform is a web service where the client makes requests to a server that processes them and returns the response.</t>
+          <t>Hardware device (miniature computer) connected to screens for content reproduction.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1925,12 +1945,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1943,7 +1963,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1953,29 +1973,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Service for querying data stored in S3 using SQL.</t>
+          <t>Service for real-time data streaming.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1985,11 +2005,13 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>49</v>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1999,7 +2021,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2007,254 +2029,258 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Object storage service for JSON documents.</t>
+          <t>The API Gateway communicates with the Core service.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45, 48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>api gateway, core</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU10, CF_M01_AU11</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>CF_M01_AU26</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>api gateway service, core service</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Service enabling bidirectional communication between the platform and players.</t>
+          <t>The API Gateway communicates with the Analytical Module.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_06', 'AU_08']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>api gateway, analytical module</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU10, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>CF_M01_AU27</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>api gateway service, analytical module</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Core layer responsible for processing information and user requests.</t>
+          <t>The Player device communicates with the API Player service.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['AU_20', 'AU_09']</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU30, CF_M01_AU13</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>CF_M01_AU31</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2273,28 +2299,28 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HTTP communication between presentation layer and API Gateway.</t>
+          <t>The Player device communicates with the Web Socket service.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>41, 42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_01', 'AU_06']</t>
+          <t>['AU_20', 'AU_10']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway</t>
+          <t>player, web socket</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2305,57 +2331,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
+          <t>CF_M01_AU30, CF_M01_AU14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway service</t>
+          <t>player, web socket</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>API Gateway</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TCP communication between API Gateway and Core.</t>
+          <t>A design pattern that allows only one component to interact between users and the services provided by the platform, handling authorization and SSL.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2365,29 +2395,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_07']</t>
+          <t>['P_03']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>api gateway, core</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>API Gateway</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2395,131 +2425,131 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11</t>
+          <t>CF_M01_AD03</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>api gateway service, core service</t>
-        </is>
-      </c>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Web Socket</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TCP communication between API Gateway and Analytics Module.</t>
+          <t>Service for bidirectional communication between the platform and players.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_08']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>api gateway, analytics module</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Web Socket</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU12</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>api gateway service, analytical module</t>
-        </is>
-      </c>
+          <t>CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>API Player</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Communication between Players and API Player.</t>
+          <t>Service responsible for communicating with players to receive status and content information.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2529,29 +2559,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_20', 'AU_09']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Api Player</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with players.</t>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2559,81 +2589,81 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU30, CF_M01_AU13</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
+          <t>CF_M01_AU13</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Analytical Module</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Communication between Players and Web Socket.</t>
+          <t>Service for obtaining and processing playlogs, connections, and platform actions.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43, 62</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_20', 'AU_10']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Analytical module</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2641,35 +2671,31 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU30, CF_M01_AU14</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>CF_M01_AU12</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2677,49 +2703,45 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The system is divided into three layers: presentation layer, business layer, and data layer.</t>
+          <t>Layer responsible for storing all system data.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
+          <t>41, 44</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2727,13 +2749,13 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2741,12 +2763,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2759,49 +2781,45 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Protocol used for communication between presentation and business layers.</t>
+          <t>Core layer responsible for processing information and business logic.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['AU_21']</t>
-        </is>
-      </c>
+          <t>41, 42, 43</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2809,13 +2827,13 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AD02</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2823,12 +2841,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2841,55 +2859,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Miniature computer device connected to screens for content reproduction.</t>
+          <t>Data integration service used for metadata cataloging.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>['AU_13']</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2897,12 +2923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2915,7 +2941,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2925,29 +2951,29 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Service for loading streaming data into data stores.</t>
+          <t>Object storage service used for the data lake.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45, 48</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2957,11 +2983,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2971,7 +2997,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2979,12 +3005,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2997,63 +3023,63 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>API Player</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Service responsible for communicating with players to receive status and content information.</t>
+          <t>Service for performing SQL queries on data stored in S3.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Api Player</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3061,12 +3087,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3079,7 +3105,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3089,25 +3115,25 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Layer responsible for storing all system data.</t>
+          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41, 44</t>
+          <t>41, 42</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3117,7 +3143,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -3131,7 +3157,7 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3139,12 +3165,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3157,228 +3183,66 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>Service for loading streaming data into data stores.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>['AU_13']</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Data integration service used for metadata management and data cataloging.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['AU_12']</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CF_M01_AU22</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Service for real-time data streaming.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['AU_12']</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>CF_M01_AU22</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3391,7 +3255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3439,7 +3303,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3449,105 +3313,105 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Database engine used for the relational database.</t>
+          <t>AWS service implementing the MySQL database.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.1751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>web socket, cloud services</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Communication between Web Socket and Cloud Services.</t>
+          <t>Backend framework used for developing microservices.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5609</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>core, database</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Communication between Core and Database.</t>
+          <t>Programming language used for development.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3558,32 +3422,32 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>core, cloud services</t>
+          <t>web platform, api gateway</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Communication between Core and Cloud Services.</t>
+          <t>The Web Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4473</v>
+        <v>0.4804</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3594,32 +3458,32 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>analytics module, cloud services</t>
+          <t>mobile platform, api gateway</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Communication between Analytics Module and Cloud Services.</t>
+          <t>The Mobile Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.466</v>
+        <v>0.4672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3630,346 +3494,314 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>analytics module, database</t>
+          <t>web socket, database</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Communication between Analytics Module and Database.</t>
+          <t>The Web Socket service communicates with the Database.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.476</v>
+        <v>0.5787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>web socket, cloud services set</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Protocol used for communication between microservices.</t>
+          <t>The Web Socket service communicates with the Cloud Services Set.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.4804</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NestJS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>core, database</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices.</t>
+          <t>The Core service communicates with the Database.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>core, cloud services set</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Programming language used for development.</t>
+          <t>The Core service communicates with the Cloud Services Set.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.6042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_35</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>analytical module, database</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Technical support department of Waapiti.</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>CF_M01_AU12</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Analytical module</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>0.0287</v>
+        <v>0.6383</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_36</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>analytical module, cloud services set</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stakeholder responsible for product value and requirements.</t>
+          <t>The Analytical Module communicates with the Cloud Services Set.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.0319</v>
+        <v>0.5977</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_37</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cloud services set, database</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Author of the project responsible for design and implementation.</t>
+          <t>The Cloud Services Set communicates with the Database.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>AWS cloud services suite</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.0227</v>
+        <v>0.3671</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_38</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clients</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>External beneficiaries of the platform.</t>
+          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>AWS cloud services suite</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.4613</v>
+        <v>0.2282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Data Lake</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
+          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AWS cloud services suite</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.2781</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Data Lake</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.441</v>
+        <v>0.4246</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +3815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4061,7 +3893,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0243</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="3">
@@ -4097,7 +3929,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5508</v>
+        <v>0.5505</v>
       </c>
     </row>
     <row r="4">
@@ -4128,18 +3960,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2881</v>
+        <v>0.2497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4149,7 +3981,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4160,70 +3992,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.07580000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>via the HTTP protocol</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4237,45 +4073,49 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5903</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4287,7 +4127,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>via the HTTP protocol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4307,73 +4147,133 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AWS cloud services suite</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cloud Services</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.7198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AWS cloud services suite</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cloud Services Set</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6069</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M01_AD03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cloud Services</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.2368</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.194</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.65</v>
+        <v>0.7609</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6842</v>
+        <v>0.7609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8148</v>
+        <v>0.7188</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8874</v>
+        <v>0.8998</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.9429</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6857</v>
       </c>
       <c r="C8" t="n">
-        <v>0.417</v>
+        <v>0.5511</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8462</v>
+        <v>0.8286</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9524</v>
+        <v>0.9667</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8636</v>
+        <v>0.7407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7037</v>
+        <v>0.7407</v>
       </c>
     </row>
     <row r="3">
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3077</v>
+        <v>0.8571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5714</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.65</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6842</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="10">
@@ -864,22 +864,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -917,25 +917,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -973,25 +973,25 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n">
         <v>36</v>
       </c>
-      <c r="C6" t="n">
-        <v>34</v>
-      </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,12 +1141,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1155,43 +1155,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6069</v>
+        <v>0.6546</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cloud Services Set</t>
+          <t>Web Platform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collection of AWS services forming a data lake for historical data processing.</t>
+          <t>Web interface for the Waapiti platform.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_01']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AWS cloud services suite</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1201,21 +1201,21 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The services used have different main functions that together allow the creation of the necessary infrastructure to manage the data on the platform. The main functions are the following: storage, data reading and data transmission.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Main business logic service of the platform.</t>
+          <t>Main service responsible for the platform's core business logic.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6757</v>
+        <v>0.7151</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Web Platform</t>
+          <t>Mobile Platform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Web interface for the Waapiti platform.</t>
+          <t>Mobile interface for the Waapiti platform.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1349,13 +1349,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>Waapiti Mobile Platform</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1379,7 +1379,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1387,12 +1387,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1401,43 +1401,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7319</v>
+        <v>0.7651</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mobile Platform</t>
+          <t>Cloud Services</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mobile interface for the Waapiti platform.</t>
+          <t>Collection of AWS services forming a data lake for historical data processing.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1447,21 +1447,23 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>42</v>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1483,7 +1485,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7946</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1497,12 +1499,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Service responsible for management, authentication, authorization, and routing requests between clients and microservices.</t>
+          <t>Service responsible for management, authentication, and authorization of users, acting as the entry point for the business layer.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>43, 44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1565,7 +1567,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8002</v>
+        <v>0.8082</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1574,12 +1576,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Relational database for storing system data.</t>
+          <t>Relational database storing system data.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1633,7 +1635,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1647,7 +1649,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1661,7 +1663,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NoSQL database service for real-time playlog storage.</t>
+          <t>NoSQL database service used for real-time playlog storage.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1671,13 +1673,13 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1720,7 +1722,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1783,13 +1785,13 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1802,7 +1804,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1863,7 +1865,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1871,7 +1873,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1899,7 +1901,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hardware device (miniature computer) connected to screens for content reproduction.</t>
+          <t>Hardware device (miniature computer) that connects screens to the platform to reproduce content.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1911,7 +1913,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1945,7 +1947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1973,7 +1975,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Service for real-time data streaming.</t>
+          <t>Streaming service for real-time data ingestion.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1983,13 +1985,13 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2029,195 +2031,199 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Amazon Athena</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The API Gateway communicates with the Core service.</t>
+          <t>Query service for analyzing data in S3.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_07']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>api gateway, core</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Amazon Athena</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>api gateway service, core service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU20</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The API Gateway communicates with the Analytical Module.</t>
+          <t>Object storage service used for the data lake.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45, 48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_08']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>api gateway, analytical module</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU12</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>api gateway service, analytical module</t>
-        </is>
-      </c>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Web Socket</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The Player device communicates with the API Player service.</t>
+          <t>Service responsible for bidirectional communication between the platform and players.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2227,29 +2233,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_20', 'AU_09']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Web Socket</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with players.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2257,992 +2263,1726 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M01_AU30, CF_M01_AU13</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
+          <t>CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Business Layer</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The Player device communicates with the Web Socket service.</t>
+          <t>Core layer responsible for processing information and business logic.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['AU_20', 'AU_10']</t>
-        </is>
-      </c>
+          <t>41, 42</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Business Layer</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_AU30, CF_M01_AU14</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>API Gateway</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A design pattern that allows only one component to interact between users and the services provided by the platform, handling authorization and SSL.</t>
+          <t>The Web Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['P_03']</t>
+          <t>['AU_04', 'AU_06']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>API Gateway</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>web platform, api gateway</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>The Web Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_AU10, CF_M01_AU08</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>CF_M01_AU35</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>api gateway service, web platform interface</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Service for bidirectional communication between the platform and players.</t>
+          <t>The Mobile Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_05', 'AU_06']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>mobile platform, api gateway</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>The Mobile Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU10, CF_M01_AU09</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>CF_M01_AU36</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>api gateway service, waapiti mobile platform</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>API Player</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service responsible for communicating with players to receive status and content information.</t>
+          <t>The API Gateway communicates with the Core service.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43, 44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Api Player</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>api gateway, core</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU10, CF_M01_AU11</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>CF_M01_AU26</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>api gateway service, core service</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Analytical Module</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Service for obtaining and processing playlogs, connections, and platform actions.</t>
+          <t>The API Gateway communicates with the Analytical Module.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>43, 62</t>
+          <t>43, 44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_06', 'AU_08']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Analytical module</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>api gateway, analytical module</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU10, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>CF_M01_AU27</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>api gateway service, analytical module</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Layer responsible for storing all system data.</t>
+          <t>The Player communicates with the API Player service.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41, 44</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_23', 'AU_09']</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU30, CF_M01_AU13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>CF_M01_AU31</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Core layer responsible for processing information and business logic.</t>
+          <t>The Player communicates with the Web Socket service.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41, 42, 43</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>['AU_23', 'AU_10']</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU30, CF_M01_AU14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>CF_M01_AU32</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Data integration service used for metadata cataloging.</t>
+          <t>The Web Socket service communicates with the Database.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_10', 'AU_11']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>web socket, database</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+          <t>The Web Socket service communicates with the Database.</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU14, CF_M01_AU15</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>CF_M01_AU38</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>web socket, sql database</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Object storage service used for the data lake.</t>
+          <t>The Web Socket service communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45, 48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_10', 'AU_12']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>AU_35</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>web socket, cloud services</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>The Web Socket service communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t xml:space="preserve"> CF_M01_AU14, CF_M01_AU16</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>CF_M01_AU37</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>web socket, aws cloud services set</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Amazon Athena</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Service for performing SQL queries on data stored in S3.</t>
+          <t>The Core service communicates with the Database.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_07', 'AU_11']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Amazon Athena</t>
-        </is>
-      </c>
+          <t>AU_36</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>core, database</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+          <t>The Core service communicates with the Database.</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU11, CF_M01_AU15</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>CF_M01_AU39</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>core service, sql database</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>The Core service communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>['AU_07', 'AU_12']</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>core, cloud services</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+          <t>The Core service communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AU11, CF_M01_AU16</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>CF_M01_AU40</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>core service, aws cloud services set</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Kinesis Data Firehose</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Service for loading streaming data into data stores.</t>
+          <t>The Analytical Module communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_08', 'AU_12']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Kinesis Data Firehose</t>
-        </is>
-      </c>
+          <t>AU_38</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>analytical module, cloud services</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>The Analytical Module communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU12, CF_M01_AU16</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
+          <t>CF_M01_AU41</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>analytical module, aws cloud services set</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AU_40</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>The Presentation Layer communicates with the Business Layer.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>['AU_01', 'AU_02']</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>AU_40</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>the presentation layer communicates with the business layer</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CF_M01_AU05, CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CF_M01_P04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>API Gateway</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A design pattern that allows only one component to interact between users and the services provided by the platform, handling authorization and SSL.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>['P_03']</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>API Gateway</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CF_M01_P04</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Service for loading streaming data into data stores.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>['AU_12']</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Data integration and catalog service for metadata management.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>['AU_12']</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CF_M01_AU12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Analytical Module</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Service responsible for obtaining and processing playlogs, connections, and platform actions.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>['AU_02']</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Analytical module</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>CF_M01_AU12</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Layer responsible for storing all system data.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>41, 44</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CF_M01_P02</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CF_M01_AU05</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>41, 42</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CF_M01_P02</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>CF_M01_AU05</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CF_M01_AU13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>API Player</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Service responsible for communicating with players to receive status and content information.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>['AU_02']</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Api Player</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>CF_M01_AU13</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CF_M01_AU43</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Database engine used for the relational database.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>['AU_11']</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CF_M01_AU15</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>CF_M01_AU43</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3255,7 +3995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3303,7 +4043,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3313,27 +4053,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS service implementing the MySQL database.</t>
+          <t>AWS service hosting the MySQL database.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="3">
@@ -3369,7 +4109,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.0755</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="4">
@@ -3411,151 +4151,147 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>web platform, api gateway</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The Web Platform communicates with the API Gateway.</t>
+          <t>Technical support department of Waapiti.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>API Gateway</t>
-        </is>
-      </c>
+          <t>CF_M01_AU26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.4804</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>mobile platform, api gateway</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The Mobile Platform communicates with the API Gateway.</t>
+          <t>Stakeholder responsible for product value and investment return.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4672</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>web socket, database</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Database.</t>
+          <t>Author of the project responsible for design and implementation.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.5787</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>web socket, cloud services set</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Cloud Services Set.</t>
+          <t>External beneficiaries of the platform.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.4804</v>
+        <v>0.4629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3566,32 +4302,28 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>core, database</t>
+          <t>analytical module, database</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Database.</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Core Service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU42</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.641</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3602,206 +4334,94 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>core, cloud services set</t>
+          <t>business layer, data layer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Cloud Services Set.</t>
+          <t>The Business Layer communicates with the Data Layer.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Core Service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.6042</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>analytical module, database</t>
-        </is>
-      </c>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Database.</t>
+          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.6383</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>analytical module, cloud services set</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Data Lake</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Cloud Services Set.</t>
+          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.5977</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>cloud services set, database</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>The Cloud Services Set communicates with the Database.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>AWS cloud services suite</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3671</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>AWS cloud services suite</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2282</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Data Lake</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4246</v>
+        <v>0.4115</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +4435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3884,7 +4504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3893,7 +4513,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0252</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="3">
@@ -3929,7 +4549,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5505</v>
+        <v>0.5516</v>
       </c>
     </row>
     <row r="4">
@@ -3960,12 +4580,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2497</v>
+        <v>0.2176</v>
       </c>
     </row>
     <row r="5">
@@ -4037,13 +4657,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.0755</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4054,68 +4674,64 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>presentation layer, business layer</t>
+          <t>presentation layer, api gateway service</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.5799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>presentation layer, api gateway service</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>via the HTTP protocol</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4127,7 +4743,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>via the HTTP protocol</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4147,7 +4763,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4179,101 +4795,65 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>core service, sql database</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+          <t>AU_39</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AWS cloud services suite</t>
+          <t>Service-oriented</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+          <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Cloud Services Set</t>
-        </is>
-      </c>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.6069</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M01_AD03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
-        <v>0.194</v>
+        <v>0.2009</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -447,14 +447,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>all elements (name | isPartOf)</t>
+          <t>all elements (units/patterns by name, connectors by unit-pair)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7609</v>
+        <v>0.7045</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7609</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7188</v>
+        <v>0.9286</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7931</v>
+        <v>0.7879</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8998</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9429</v>
+        <v>0.931</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6857</v>
+        <v>0.7931</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5511</v>
+        <v>0.8115</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8286</v>
+        <v>0.8276</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9667</v>
+        <v>0.5385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -559,10 +559,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" t="n">
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -623,19 +621,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7407</v>
+        <v>0.92</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7407</v>
+        <v>0.8214</v>
       </c>
     </row>
     <row r="3">
@@ -648,13 +646,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0.75</v>
@@ -663,23 +661,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>connector (unit-pairs)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8571</v>
+        <v>0.3125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.7143</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,7 +713,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -725,77 +723,101 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>True Positives (matched)</t>
+          <t>True Positives (matched elements)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Validated correct (name for units/patterns, isPartOf for connectors)</t>
+          <t>Named correct (units/patterns by name)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>False Positives</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>11</v>
+          <t>Connector unit-pairs (GT / LLM)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7 / 16</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>False Negatives</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11</v>
+          <t>Connector pair TP (recall / precision)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5 / 5</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Precision (all elements; units/patterns by name, connectors by isPartOf)</t>
+          <t>False Positives</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7609</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Recall (all elements; units/patterns by name, connectors by isPartOf)</t>
+          <t>False Negatives</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7609</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Precision (units/patterns by name, connectors by unit-pair)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7045</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recall (units/patterns by name, connectors by unit-pair)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7949000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Match threshold (cosine)</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.35</v>
+      <c r="B12" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -861,25 +883,25 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
         <v>29</v>
-      </c>
-      <c r="C2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D2" t="n">
-        <v>23</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -889,25 +911,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -917,25 +939,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -945,25 +967,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
         <v>29</v>
-      </c>
-      <c r="H5" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -973,25 +995,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
         <v>29</v>
-      </c>
-      <c r="H6" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1004,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1019,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,12 +1163,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1155,67 +1177,63 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6546</v>
+        <v>0.7799</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Web Platform</t>
+          <t>User</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Web interface for the Waapiti platform.</t>
+          <t>El client és l’usuari de la plataforma.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['AU_01']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>The client is the user of the platform</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU01</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1223,12 +1241,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1237,43 +1255,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6583</v>
+        <v>0.8603</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Main service responsible for the platform's core business logic.</t>
+          <t>Per la infraestructura es farà ús dels serveis cloud d’AWS.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1283,21 +1301,23 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>44</v>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1310,7 +1330,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1319,31 +1339,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7151</v>
+        <v>0.8605</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mobile Platform</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mobile interface for the Waapiti platform.</t>
+          <t>Servei Core: Aquest servei s’encarrega de realitzar la lògica de negoci de la plataforma, seria el nucli principal de la plataforma.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_01']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1355,7 +1375,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1365,21 +1385,21 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1387,12 +1407,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1401,11 +1421,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7651</v>
+        <v>0.8633</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cloud Services</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1415,12 +1435,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collection of AWS services forming a data lake for historical data processing.</t>
+          <t>Base de dades: La base de dades utilitzada és una base de dades MySQL que s’encarrega d’emmagatzemar totes les dades necessàries per al funcionament del sistema.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1431,29 +1451,27 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>SQL database</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>44</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1463,7 +1481,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1471,7 +1489,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1485,7 +1503,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1499,23 +1517,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Service responsible for management, authentication, and authorization of users, acting as the entry point for the business layer.</t>
+          <t>L’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>43, 44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['P_03']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1553,12 +1571,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1567,21 +1585,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8082</v>
+        <v>0.9573</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>API Player</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Relational database storing system data.</t>
+          <t>Api Player: Aquest servei s’encarrega de comunicar-se amb els players rebent tota la informació corresponent a aquest.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1591,29 +1609,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Api Player</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1621,13 +1639,13 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1635,12 +1653,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1649,67 +1667,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.9891</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DynamoDB</t>
+          <t>Analytical Module</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NoSQL database service used for real-time playlog storage.</t>
+          <t>Mòdul analític: Aquest servei és el servei que s’ha començat a desenvolupar durant el desenvolupament d’aquest TFG.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45, 48</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1717,12 +1735,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1735,63 +1753,67 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The system is divided into three layers: presentation layer, business layer, and data layer.</t>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>['AU_02']</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>The document labels this as a 'patró de disseny de microserveis' (microservices design pattern). While it is a pattern used in microservices, it is classified here as a Design Pattern as per the provided definitions.</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1799,17 +1821,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1817,55 +1839,63 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The platform is a web service where the client makes requests to a server that processes them and returns the response.</t>
+          <t>La base de dades utilitzada és una base de dades MySQL.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>['AU_09']</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CF_M01_AU15</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1873,12 +1903,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1901,7 +1931,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hardware device (miniature computer) that connects screens to the platform to reproduce content.</t>
+          <t>Un player consisteix en un dispositiu que pot ser intern o extern, que permet a les pantalles reproduir continguts.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1913,7 +1943,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1939,7 +1969,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1947,12 +1977,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1965,7 +1995,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1975,12 +2005,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Streaming service for real-time data ingestion.</t>
+          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1991,13 +2021,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2007,13 +2037,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>49</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2023,7 +2051,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2031,12 +2059,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2049,63 +2077,63 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Query service for analyzing data in S3.</t>
+          <t>Capa de presentació: És la capa que s’encarrega de mostrar la informació a l’usuari.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2113,12 +2141,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2131,7 +2159,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2141,29 +2169,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Object storage service used for the data lake.</t>
+          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45, 48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2173,21 +2201,21 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2195,172 +2223,176 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Service responsible for bidirectional communication between the platform and players.</t>
+          <t>L’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42,43</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_04', 'AU_01']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>api gateway, presentation layer</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>CF_M01_AU25</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Core layer responsible for processing information and business logic.</t>
+          <t>El servei Api Gateway [...] processa les peticions per poder enviar-les al servei Core i al mòdul analític.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>['AU_04', 'AU_05', 'AU_06']</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Business Layer</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>api gateway, core, analytical module</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>CF_M01_AU26</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>api gateway service, core service, analytical module</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2379,28 +2411,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The Web Platform communicates with the API Gateway.</t>
+          <t>Api Player: Aquest servei s’encarrega de comunicar-se amb els players rebent tota la informació corresponent a aquest.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_06']</t>
+          <t>['AU_07', 'AU_18']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>web platform, api gateway</t>
+          <t>api player, player</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2411,877 +2443,875 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>The Web Platform communicates with the API Gateway.</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU08</t>
+          <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>api gateway service, web platform interface</t>
+          <t>player, api player</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU36</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The Mobile Platform communicates with the API Gateway.</t>
+          <t>Com a framework es farà ús de NestJS.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_05', 'AU_06']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>mobile platform, api gateway</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>The Mobile Platform communicates with the API Gateway.</t>
+          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU09</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU36</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>api gateway service, waapiti mobile platform</t>
-        </is>
-      </c>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Web Socket</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The API Gateway communicates with the Core service.</t>
+          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>43, 44</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_07']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>api gateway, core</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Web Socket</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>api gateway service, core service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The API Gateway communicates with the Analytical Module.</t>
+          <t>Amazon S3: Aquest és el servei d’emmagatzament d’objectes d’AWS.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>43, 44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_08']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>api gateway, analytical module</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU12</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>api gateway service, analytical module</t>
-        </is>
-      </c>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The Player communicates with the API Player service.</t>
+          <t>El servei d’AWS Glue és un servei d’integració de dades sense servidor.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_23', 'AU_09']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with players.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M01_AU30, CF_M01_AU13</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Business Layer</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>The Player communicates with the Web Socket service.</t>
+          <t>Capa de negoci: Aquesta capa és el nucli de l’aplicació, que s’encarrega de processar tota la informació.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_23', 'AU_10']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Business Layer</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_AU30, CF_M01_AU14</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_AU38</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Database.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['AU_10', 'AU_11']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>web socket, database</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Database.</t>
+          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M01_AU14, CF_M01_AU15</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_AU38</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>web socket, sql database</t>
-        </is>
-      </c>
+          <t>CF_M01_P02</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_35</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_AU37</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Cloud Services.</t>
+          <t>Kinesis Data Streams és un servei de processament i ingesta de dades dirigit especialment al streaming de dades.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_10', 'AU_12']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>web socket, cloud services</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Cloud Services.</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>42</v>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CF_M01_AU14, CF_M01_AU16</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_AU37</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>web socket, aws cloud services set</t>
-        </is>
-      </c>
+          <t>CF_M01_AU22</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_36</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_AU39</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Database.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['AU_07', 'AU_11']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_36</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>core, database</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Database.</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>CF_M01_AU11, CF_M01_AU15</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_AU39</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>core service, sql database</t>
-        </is>
-      </c>
+          <t>CF_M01_P01</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_37</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_AU40</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Cloud Services.</t>
+          <t>DynamoDB: Aquest servei és una base de dades no relacional d’AWS.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_07', 'AU_12']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>core, cloud services</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Cloud Services.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M01_AU11, CF_M01_AU16</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_AU40</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>core service, aws cloud services set</t>
-        </is>
-      </c>
+          <t>CF_M01_AU18</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_38</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M01_AU41</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Cloud Services.</t>
+          <t>Amb el llenguatge Typescript.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_08', 'AU_12']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_38</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>analytical module, cloud services</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Cloud Services.</t>
+          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M01_AU12, CF_M01_AU16</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M01_AU41</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>analytical module, aws cloud services set</t>
-        </is>
-      </c>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_40</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>The Presentation Layer communicates with the Business Layer.</t>
+          <t>Capa de dades: És la capa que s’encarrega d'emmagatzemar totes les dades.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3291,65 +3321,61 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_01', 'AU_02']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_40</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU06</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3357,63 +3383,63 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A design pattern that allows only one component to interact between users and the services provided by the platform, handling authorization and SSL.</t>
+          <t>El servei de Kinesis Data Firehose té com a funció principal la càrrega de grans quantitats de dades en magatzems de dades.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['P_03']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3421,12 +3447,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3439,7 +3465,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3449,29 +3475,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Service for loading streaming data into data stores.</t>
+          <t>La comunicació entre el servei de l’Api Gateway és mitjançant el protocol de comunicació TCP.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3481,508 +3507,24 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU26,CF_M01_AU27</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Data integration and catalog service for metadata management.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>['AU_12']</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CF_M01_AU12</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Analytical Module</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Service responsible for obtaining and processing playlogs, connections, and platform actions.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['AU_02']</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Analytical module</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>CF_M01_AU12</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Layer responsible for storing all system data.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>41, 44</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>CF_M01_P02</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>CF_M01_AU05</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>41, 42</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>CF_M01_P02</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>CF_M01_AU05</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>CF_M01_AU13</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>API Player</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Service responsible for communicating with players to receive status and content information.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>['AU_02']</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Api Player</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>CF_M01_AU13</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>CF_M01_AU43</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>MySQL</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Database engine used for the relational database.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>['AU_11']</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>MySQL</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>CF_M01_AU15</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>CF_M01_AU43</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3995,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4043,7 +3585,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4059,79 +3601,79 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS service hosting the MySQL database.</t>
+          <t>Aquesta base de dades està implementada en el servei RDS, que és un servei de base de dades relacional distribuït d’AWS.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.6606</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Cloud Storage</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices.</t>
+          <t>Conjunt de serveis cloud AWS: L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.0762</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Programming language used for development.</t>
+          <t>la capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4139,159 +3681,155 @@
           <t>CF_M01_AU30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>core, database, cloud storage</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Technical support department of Waapiti.</t>
+          <t>Servei Core: [...] Principalment, interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M01_AU11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Core Service</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.0315</v>
+        <v>0.7564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>analytical module, cloud storage, database</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stakeholder responsible for product value and investment return.</t>
+          <t>Mòdul analític: [...] Principalment, aquest servei interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.0336</v>
+        <v>0.6844</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>web socket, player, database, cloud storage</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Author of the project responsible for design and implementation.</t>
+          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells. Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.0219</v>
+        <v>0.8249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Clients</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>web socket, core, kinesis data firehose, cloud storage</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>External beneficiaries of the platform.</t>
+          <t>El microservei WebSocket [...] s’encarrega de rebre la informació dels players. Mentre que l’audit trail té com a generador el Core [...] Per part dels consumidors tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.4629</v>
+        <v>0.7445000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_39</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4302,28 +3840,32 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>analytical module, database</t>
+          <t>amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Database.</t>
+          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU42</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.7753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_41</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4334,94 +3876,26 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>business layer, data layer</t>
+          <t>aws glue, amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Business Layer communicates with the Data Layer.</t>
+          <t>El servei d’AWS Glue [...] treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>0.745</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AWS cloud services set</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.261</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Data Lake</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4115</v>
+        <v>0.7893</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +3909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4483,7 +3957,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU01</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4493,86 +3967,86 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0234</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>customer, server</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for processing user requests.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5516</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>customer, server</t>
-        </is>
-      </c>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4580,90 +4054,94 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.2176</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.7358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Waapiti Mobile Platform</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.0762</v>
+        <v>0.6101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4674,64 +4152,64 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway service</t>
+          <t>presentation layer, business layer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.5799</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>via the HTTP protocol</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.8249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4739,121 +4217,65 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AWSS RDS</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU42</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>core service, sql database</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>The Analytical Module communicates with the Database.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_39</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>0.2009</v>
+        <v>0.703</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7045</v>
+        <v>0.7317</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9286</v>
+        <v>0.9615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7879</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9714</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.931</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7931</v>
+        <v>0.931</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8115</v>
+        <v>0.8635</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8276</v>
+        <v>0.8966</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5385</v>
+        <v>0.8077</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -559,8 +559,10 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -624,16 +626,16 @@
         <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8214</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="3">
@@ -646,13 +648,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F3" t="n">
         <v>0.75</v>
@@ -668,13 +670,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3125</v>
+        <v>0.3333</v>
       </c>
       <c r="F4" t="n">
         <v>0.7143</v>
@@ -723,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -743,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -754,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 16</t>
+          <t>7 / 15</t>
         </is>
       </c>
     </row>
@@ -777,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -797,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7045</v>
+        <v>0.7317</v>
       </c>
     </row>
     <row r="11">
@@ -807,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +888,19 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
         <v>29</v>
@@ -914,7 +916,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
         <v>29</v>
@@ -926,7 +928,7 @@
         <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
         <v>29</v>
@@ -942,7 +944,7 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
         <v>29</v>
@@ -954,7 +956,7 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
         <v>29</v>
@@ -970,7 +972,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
         <v>29</v>
@@ -982,7 +984,7 @@
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
         <v>29</v>
@@ -998,7 +1000,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>27</v>
@@ -1010,7 +1012,7 @@
         <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
         <v>29</v>
@@ -1026,13 +1028,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1163,7 +1165,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1191,7 +1193,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>El client és l’usuari de la plataforma.</t>
+          <t>The client is the user of the platform.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1203,7 +1205,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -1241,12 +1243,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1255,43 +1257,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8603</v>
+        <v>0.8605</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Per la infraestructura es farà ús dels serveis cloud d’AWS.</t>
+          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1301,23 +1303,21 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>44</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1339,21 +1339,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8605</v>
+        <v>0.8633</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servei Core: Aquest servei s’encarrega de realitzar la lògica de negoci de la plataforma, seria el nucli principal de la plataforma.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1363,29 +1363,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>SQL database</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1393,13 +1393,13 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1407,12 +1407,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1421,11 +1421,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8633</v>
+        <v>0.9241</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>AWS Cloud Services</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1435,43 +1435,45 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Base de dades: La base de dades utilitzada és una base de dades MySQL que s’encarrega d’emmagatzemar totes les dades necessàries per al funcionament del sistema.</t>
+          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>44</v>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1481,7 +1483,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1489,7 +1491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1517,23 +1519,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>L’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>43, 44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['P_03']</t>
+          <t>['AU_03', 'P_03', 'P_04']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1571,7 +1573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1599,7 +1601,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Api Player: Aquest servei s’encarrega de comunicar-se amb els players rebent tota la informació corresponent a aquest.</t>
+          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1609,13 +1611,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1653,12 +1655,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1667,67 +1669,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9891</v>
+        <v>0.9839</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Analytical Module</t>
+          <t>DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mòdul analític: Aquest servei és el servei que s’ha començat a desenvolupar durant el desenvolupament d’aquest TFG.</t>
+          <t>This service is a non-relational database of AWS.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45, 48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1735,85 +1737,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.9891</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Analytical Module</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+          <t>This service is the service that has begun to be developed during the development of this TFG.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>The document labels this as a 'patró de disseny de microserveis' (microservices design pattern). While it is a pattern used in microservices, it is classified here as a Design Pattern as per the provided definitions.</t>
-        </is>
-      </c>
+          <t>['AU_03', 'P_04']</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1821,17 +1819,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1839,63 +1837,63 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>La base de dades utilitzada és una base de dades MySQL.</t>
+          <t>Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['P_02', 'AU_05']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1903,7 +1901,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1931,7 +1929,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Un player consisteix en un dispositiu que pot ser intern o extern, que permet a les pantalles reproduir continguts.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to play content.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1943,7 +1941,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1977,7 +1975,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2005,7 +2003,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
+          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2015,13 +2013,13 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2059,7 +2057,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2087,7 +2085,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Capa de presentació: És la capa que s’encarrega de mostrar la informació a l’usuari.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2103,7 +2101,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2169,17 +2167,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
+          <t>Communication protocol used between the client and the server.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>41, 42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_02', 'AU_05']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -2223,7 +2221,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2247,28 +2245,28 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>L’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
+          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42,43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_01']</t>
+          <t>['AU_02', 'AU_05']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>api gateway, presentation layer</t>
+          <t>presentation layer, api gateway</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2305,7 +2303,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2329,7 +2327,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>El servei Api Gateway [...] processa les peticions per poder enviar-les al servei Core i al mòdul analític.</t>
+          <t>The Api Gateway processes requests to send them to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2339,13 +2337,13 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_05', 'AU_06']</t>
+          <t>['AU_05', 'AU_06', 'AU_07']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2387,7 +2385,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2411,7 +2409,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Api Player: Aquest servei s’encarrega de comunicar-se amb els players rebent tota la informació corresponent a aquest.</t>
+          <t>The Api Player communicates with players receiving all information corresponding to it. [...] This information is processed and stored.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2421,13 +2419,13 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_07', 'AU_18']</t>
+          <t>['AU_08', 'AU_22']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2469,67 +2467,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>NestJS</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Com a framework es farà ús de NestJS.</t>
+          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['AU_09', 'AU_22']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>NestJS</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>web socket, player</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2537,26 +2531,30 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2569,49 +2567,49 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells.</t>
+          <t>Framework used to develop the different services that interact with each other.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_05', 'AU_06', 'AU_07', 'AU_08', 'AU_09']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2619,13 +2617,13 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2633,12 +2631,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2651,63 +2649,63 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Amazon S3: Aquest és el servei d’emmagatzament d’objectes d’AWS.</t>
+          <t>This service is responsible for carrying out the communication between the platform and the players.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2715,12 +2713,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2733,7 +2731,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2743,29 +2741,29 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>El servei d’AWS Glue és un servei d’integració de dades sense servidor.</t>
+          <t>This is the object storage service of AWS.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45, 48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2775,11 +2773,11 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2789,7 +2787,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2797,12 +2795,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2815,63 +2813,63 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Capa de negoci: Aquesta capa és el nucli de l’aplicació, que s’encarrega de processar tota la informació.</t>
+          <t>The AWS Glue service is a serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2879,17 +2877,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2897,17 +2895,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2917,29 +2915,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2947,13 +2945,13 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2961,17 +2959,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2979,65 +2977,63 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams és un servei de processament i ingesta de dades dirigit especialment al streaming de dades.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
+          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>41</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3045,17 +3041,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3063,55 +3059,65 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>Kinesis Data Streams is a data processing and ingestion service aimed especially at data streaming.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>['AU_11']</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3119,17 +3125,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3137,63 +3143,55 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DynamoDB: Aquest servei és una base de dades no relacional d’AWS.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['AU_12']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3201,7 +3199,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3229,23 +3227,23 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Amb el llenguatge Typescript.</t>
+          <t>Programming language used for the development of the backend.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3283,7 +3281,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3311,7 +3309,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Capa de dades: És la capa que s’encarrega d'emmagatzemar totes les dades.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3327,7 +3325,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3365,7 +3363,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3393,7 +3391,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>El servei de Kinesis Data Firehose té com a funció principal la càrrega de grans quantitats de dades en magatzems de dades.</t>
+          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3403,13 +3401,13 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -3475,7 +3473,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>La comunicació entre el servei de l’Api Gateway és mitjançant el protocol de comunicació TCP.</t>
+          <t>Communication protocol used between the services.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3485,7 +3483,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3537,7 +3535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3585,73 +3583,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>core, database, aws cloud services</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aquesta base de dades està implementada en el servei RDS, que és un servei de base de dades relacional distribuït d’AWS.</t>
+          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7803</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cloud Storage</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>analytical module, aws cloud services, database</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Conjunt de serveis cloud AWS: L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics.</t>
+          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7937</v>
+        <v>0.7214</v>
       </c>
     </row>
     <row r="4">
@@ -3668,28 +3666,28 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway</t>
+          <t>web socket, database, aws cloud services</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>la capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
+          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.7845</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3700,32 +3698,32 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>core, database, cloud storage</t>
+          <t>kinesis data streams, web socket, core</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Servei Core: [...] Principalment, interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
+          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers. [...] In the case of playlogs the generator is the WebSocket microservice. [...] While the audit trail has as a generator the Core.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7564</v>
+        <v>0.7364000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3736,26 +3734,26 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>analytical module, cloud storage, database</t>
+          <t>kinesis data firehose, aws cloud services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mòdul analític: [...] Principalment, aquest servei interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
+          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in S3.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6844</v>
+        <v>0.8252</v>
       </c>
     </row>
     <row r="7">
@@ -3772,22 +3770,26 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>web socket, player, database, cloud storage</t>
+          <t>analytical module, amazon athena</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells. Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
+          <t>The analytical module uses the AWS Athena service to perform queries on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>0.8249</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="8">
@@ -3804,98 +3806,62 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>web socket, core, kinesis data firehose, cloud storage</t>
+          <t>analytical module, database</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El microservei WebSocket [...] s’encarrega de rebre la informació dels players. Mentre que l’audit trail té com a generador el Core [...] Per part dels consumidors tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
+          <t>The analytical module also has the database service, which is responsible for connecting and performing queries to the platform's database.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>amazon athena, amazon s3</t>
-        </is>
-      </c>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
+          <t>L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema... les diferents capes que formen el sistema es componen de diversos serveis que interactuen entre si.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.7753</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>aws glue, amazon athena, amazon s3</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>El servei d’AWS Glue [...] treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7893</v>
+        <v>0.7454</v>
       </c>
     </row>
   </sheetData>
@@ -4018,16 +3984,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.7941</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="4">
@@ -4126,7 +4088,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4162,7 +4124,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4177,33 +4139,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0.8249</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="9">
@@ -4235,11 +4201,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amazon RDS</t>
+          <t>AWS Cloud Services</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.742</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7317</v>
+        <v>0.6744</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7692</v>
+        <v>0.7436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9615</v>
+        <v>0.963</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7879</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9722</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.9643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.931</v>
+        <v>0.9286</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8635</v>
+        <v>0.8739</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8966</v>
+        <v>0.8571</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8077</v>
+        <v>0.8333</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7857</v>
+        <v>0.8214</v>
       </c>
     </row>
     <row r="3">
@@ -670,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333</v>
+        <v>0.1875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7143</v>
+        <v>0.4286</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 15</t>
+          <t>7 / 16</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5 / 5</t>
+          <t>3 / 3</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7317</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7692</v>
+        <v>0.7436</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
         <v>26</v>
       </c>
-      <c r="D2" t="n">
-        <v>25</v>
-      </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +1000,22 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
         <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,12 +1243,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1257,53 +1257,53 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8605</v>
+        <v>0.8544</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
+          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>AWSS RDS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1311,13 +1311,13 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1339,21 +1339,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8633</v>
+        <v>0.8605</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1363,29 +1363,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1393,13 +1393,13 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1407,12 +1407,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1421,11 +1421,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9241</v>
+        <v>0.8633</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS Cloud Services</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1451,29 +1451,27 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>SQL database</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>44</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1483,7 +1481,7 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1491,12 +1489,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1505,11 +1503,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9241</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>AWS Cloud Services</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1519,29 +1517,29 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
+          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>43, 44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_03', 'P_04']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>API Gateway Service</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1551,21 +1549,23 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>44</v>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1573,12 +1573,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1587,11 +1587,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9573</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>API Player</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1601,29 +1601,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43, 44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_03', 'P_03', 'P_04']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Api Player</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1647,7 +1647,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1683,17 +1683,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>This service is a non-relational database of AWS.</t>
+          <t>This service is a non-relational database from AWS.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45, 48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_11']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1901,12 +1901,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1919,55 +1919,63 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Api Player</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to play content.</t>
+          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>['AU_03', 'P_04']</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Api Player</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CF_M01_AU06</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1975,12 +1983,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1993,7 +2001,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2003,29 +2011,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
+          <t>The database used is a MySQL database.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_11']</t>
+          <t>['AU_10']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2035,21 +2043,21 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2057,12 +2065,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2075,63 +2083,63 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2139,12 +2147,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2157,49 +2165,49 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Communication protocol used between the client and the server.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>41, 42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_05']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -2207,13 +2215,13 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M01_AU24, CF_M01_AU25</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2221,84 +2229,80 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_05']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>presentation layer, api gateway</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
+          <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>presentation layer, api gateway service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU03</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2308,7 +2312,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2327,17 +2331,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The Api Gateway processes requests to send them to the Core service and the analytical module.</t>
+          <t>la capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_05', 'AU_06', 'AU_07']</t>
+          <t>['AU_02', 'AU_05']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2348,7 +2352,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>api gateway, core, analytical module</t>
+          <t>presentation layer, api gateway</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2359,38 +2363,38 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>api gateway service, core service, analytical module</t>
+          <t>presentation layer, api gateway service</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2409,7 +2413,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The Api Player communicates with players receiving all information corresponding to it. [...] This information is processed and stored.</t>
+          <t>Aquest servei [Api Gateway] s’encarrega de la gestió, autenticació i autorització dels usuaris de la plataforma. Defineix totes les rutes de l’API REST i processa les peticions per poder enviar-les al servei Core i al mòdul analític.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2419,18 +2423,18 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_08', 'AU_22']</t>
+          <t>['AU_05', 'AU_06', 'AU_07']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>api player, player</t>
+          <t>api gateway, core, analytical module</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2441,89 +2445,93 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with players.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_AU27, CF_M01_AU13</t>
+          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>player, api player</t>
+          <t>api gateway service, core service, analytical module</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players.</t>
+          <t>As a framework, NestJS will be used.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_09', 'AU_22']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>web socket, player</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -2531,30 +2539,26 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU27, CF_M01_AU14</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2567,49 +2571,49 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Framework used to develop the different services that interact with each other.</t>
+          <t>This service is responsible for carrying out the communication between the platform and the players.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_05', 'AU_06', 'AU_07', 'AU_08', 'AU_09']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2617,13 +2621,13 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2631,12 +2635,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2649,63 +2653,63 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the communication between the platform and the players.</t>
+          <t>This is the object storage service of AWS.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2713,12 +2717,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2731,7 +2735,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2741,29 +2745,29 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>This is the object storage service of AWS.</t>
+          <t>The AWS Glue service is a serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45, 48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_11']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2773,11 +2777,11 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2787,7 +2791,7 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2795,12 +2799,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2813,63 +2817,63 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>The AWS Glue service is a serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_11']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2877,17 +2881,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2895,17 +2899,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>This layer is the core of the application and is responsible for processing all the information.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,29 +2919,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2945,13 +2949,13 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2959,17 +2963,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2977,63 +2981,65 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
+          <t>Kinesis Data Streams is a data processing and ingestion service specifically aimed at data streaming.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>41</v>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3041,17 +3047,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3059,65 +3065,55 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams is a data processing and ingestion service aimed especially at data streaming.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['AU_11']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3125,17 +3121,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3143,55 +3139,63 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>With the language Typescript.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3199,12 +3203,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3217,63 +3221,63 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Programming language used for the development of the backend.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3281,12 +3285,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3299,63 +3303,63 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data.</t>
+          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3363,12 +3367,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3381,7 +3385,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3391,29 +3395,25 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
+          <t>The communication between the API Gateway service is through the TCP communication protocol.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['AU_11']</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3423,106 +3423,24 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU26,CF_M01_AU27</t>
         </is>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Communication protocol used between the services.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>CF_M01_AU26,CF_M01_AU27</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3583,7 +3501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3599,7 +3517,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>Principalment, [Core] interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3613,13 +3531,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7699</v>
+        <v>0.7533</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3635,7 +3553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>Principalment, aquest servei [Analytical Module] interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3649,13 +3567,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7214</v>
+        <v>0.7271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3671,7 +3589,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3681,13 +3599,13 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.799</v>
+        <v>0.8186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3703,7 +3621,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers. [...] In the case of playlogs the generator is the WebSocket microservice. [...] While the audit trail has as a generator the Core.</t>
+          <t>En el cas dels generadors [de Kinesis Data Streams], aquests serien els diferents microserveis de NestJS que tenen la informació sobre els playlogs o les accions en plataforma. En el cas dels playlogs el generador el microservei WebSocket [...] Mentre que l’audit trail té com a generador el Core.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3717,13 +3635,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3734,12 +3652,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>kinesis data firehose, aws cloud services</t>
+          <t>kinesis data streams, kinesis data firehose, amazon s3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in S3.</t>
+          <t>Per part dels consumidors [de Kinesis Data Streams] tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3753,13 +3671,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8252</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3770,12 +3688,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>analytical module, amazon athena</t>
+          <t>amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The analytical module uses the AWS Athena service to perform queries on data stored in Amazon S3.</t>
+          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3789,13 +3707,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7654</v>
+        <v>0.7753</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3806,26 +3724,26 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>analytical module, database</t>
+          <t>aws glue, amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The analytical module also has the database service, which is responsible for connecting and performing queries to the platform's database.</t>
+          <t>L’ús d’aquesta [AWS Glue Data Catalog] ha sigut necessària per poder emmagatzemar les metadades de les dades del projecte [...] D’aquesta manera treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7284</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="9">
@@ -3875,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3923,92 +3841,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for processing user requests.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>User</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8237</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>customer, server</t>
-        </is>
-      </c>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0.823</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>customer, server</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4016,7 +3938,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4025,49 +3947,49 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7358</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4077,7 +3999,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -4088,159 +4010,187 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6101</v>
+        <v>0.7358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Waapiti Mobile Platform</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.887</v>
+        <v>0.6101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MySQL</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7872</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AWSS RDS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AWS Cloud Services</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.658</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>This service is responsible for communicating between the platform and the players.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.8186</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>0.703</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6744</v>
+        <v>0.6415</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7436</v>
+        <v>0.8718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.963</v>
+        <v>0.8529</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7879</v>
+        <v>0.8788</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9643</v>
+        <v>0.7188</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9286</v>
+        <v>0.9062</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8739</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8571</v>
+        <v>0.8125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8333</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.8667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8214</v>
+        <v>0.9286</v>
       </c>
     </row>
     <row r="3">
@@ -670,16 +670,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1875</v>
+        <v>0.2632</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4286</v>
+        <v>0.7143</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 16</t>
+          <t>7 / 19</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3 / 3</t>
+          <t>5 / 5</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6744</v>
+        <v>0.6415</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7436</v>
+        <v>0.8718</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +1000,22 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
         <v>32</v>
-      </c>
-      <c r="D6" t="n">
-        <v>27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>24</v>
-      </c>
-      <c r="F6" t="n">
-        <v>24</v>
-      </c>
-      <c r="G6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H6" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AU01</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1179,63 +1179,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7799</v>
+        <v>0.7771</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>AWS RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform.</t>
+          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>['AU_12']</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>AWSS RDS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform</t>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M01_AU01</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1243,12 +1247,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1257,67 +1261,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8544</v>
+        <v>0.8012</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Mobile Platform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
+          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_10']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>AWSS RDS</t>
+          <t>Waapiti Mobile Platform</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1325,12 +1329,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1339,11 +1343,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8605</v>
+        <v>0.8139</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Database Service</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1363,29 +1367,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>SQL database</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1393,13 +1397,13 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1407,12 +1411,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1421,67 +1425,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8633</v>
+        <v>0.8436</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>The communication between the two components is carried out through the internet using the REST API model.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1503,37 +1503,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9241</v>
+        <v>0.8603</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS Cloud Services</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
+          <t>For the infrastructure, the cloud services of AWS will be used.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['AU_04']</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1573,12 +1569,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1587,43 +1583,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8605</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
+          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>43, 44</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_03', 'P_04']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>API Gateway Service</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1633,7 +1629,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1647,7 +1643,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1655,12 +1651,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1669,67 +1665,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9839</v>
+        <v>0.9185</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DynamoDB</t>
+          <t>Web Platform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS.</t>
+          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1742,7 +1738,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1751,31 +1747,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9891</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Analytical Module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>This service is the service that has begun to be developed during the development of this TFG.</t>
+          <t>The only component that interacts directly with the presentation layer is the Api Gateway module.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_03', 'P_03']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1787,7 +1783,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1811,7 +1807,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1819,81 +1815,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.9573</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>API Player</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+          <t>This service is responsible for communicating with the players by receiving all the information corresponding to it.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['P_02', 'AU_05']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Api Player</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1901,12 +1897,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1915,67 +1911,67 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9839</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Api Player</t>
+          <t>DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
+          <t>This service is a non-relational database of AWS.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Api Player</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1983,12 +1979,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1997,21 +1993,21 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9891</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Analytical Module</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database.</t>
+          <t>The analytical module has as its main function to obtain and process the data of the playlogs, the connections and the actions in the platform.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2021,29 +2017,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_10']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2051,13 +2047,13 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2065,17 +2061,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2083,63 +2079,63 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['P_02', 'AU_07']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2147,12 +2143,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2165,63 +2161,63 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>The database used is a MySQL database.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2229,12 +2225,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2247,59 +2243,55 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
+          <t>A player consists of a device that can be internal or external, which allows the screens to play content.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>CF_M01_AU24, CF_M01_AU25</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2312,36 +2304,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Amazon Athena</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>la capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
+          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_05']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2350,133 +2346,129 @@
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>presentation layer, api gateway</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Amazon Athena</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>presentation layer, api gateway service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU20</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aquest servei [Api Gateway] s’encarrega de la gestió, autenticació i autorització dels usuaris de la plataforma. Defineix totes les rutes de l’API REST i processa les peticions per poder enviar-les al servei Core i al mòdul analític.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_05', 'AU_06', 'AU_07']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>api gateway, core, analytical module</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>api gateway service, core service, analytical module</t>
-        </is>
-      </c>
+          <t>CF_M01_AU05</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2489,7 +2481,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2499,29 +2491,25 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>As a framework, NestJS will be used.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2531,21 +2519,21 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2553,258 +2541,258 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the communication between the platform and the players.</t>
+          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_02', 'AU_07']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Web Socket</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>the presentation layer communicates with the business layer more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>CF_M01_AU25</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>This is the object storage service of AWS.</t>
+          <t>The Api Gateway service processes requests to send them to the Core service and the Analytical Module.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_07', 'AU_08', 'AU_09']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>api gateway, core, analytical module</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>CF_M01_AU26</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>api gateway service, core service, analytical module</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The AWS Glue service is a serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources.</t>
+          <t>The Api Player service is responsible for communicating with the players by receiving all the information corresponding to it. [...] This information is processed and stored.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_10', 'AU_30']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
+          <t>AU_36</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>api player, player</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>CF_M01_AU28</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2817,63 +2805,63 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>This layer is the core of the application and is responsible for processing all the information.</t>
+          <t>As a framework, NestJS will be used.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2881,17 +2869,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2899,63 +2887,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
+          <t>This service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2963,12 +2951,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2981,7 +2969,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2991,29 +2979,29 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams is a data processing and ingestion service specifically aimed at data streaming.</t>
+          <t>This is the object storage service of AWS.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3023,13 +3011,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>45</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3039,7 +3025,7 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3047,17 +3033,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3065,55 +3051,63 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>The AWS Glue service is a serverless data integration service.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>['AU_15']</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3121,12 +3115,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3139,63 +3133,63 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>With the language Typescript.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3203,17 +3197,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3221,17 +3215,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3241,29 +3235,29 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3271,13 +3265,13 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3285,12 +3279,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3303,7 +3297,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3313,29 +3307,29 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
+          <t>Kinesis Data Streams is a data processing and ingestion service specifically aimed at data streaming.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3345,11 +3339,13 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>51</v>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -3359,7 +3355,7 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3367,17 +3363,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF_M01_AU31</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3385,62 +3381,382 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>The communication between the API Gateway service is through the TCP communication protocol.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>CF_M01_AU26,CF_M01_AU27</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
+          <t>CF_M01_P01</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>With the Typescript language.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>It is the layer that is responsible for storing all the data.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>['P_02']</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CF_M01_P02</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>['AU_15']</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>The communication between the Api Gateway service is through the TCP communication protocol.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CF_M01_AU26,CF_M01_AU27</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>CF_M01_AU31</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3453,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3501,73 +3817,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>core, database, aws cloud services</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Principalment, [Core] interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
+          <t>The client is the user of the platform.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7533</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>analytical module, aws cloud services, database</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data Lake Service</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Principalment, aquest servei [Analytical Module] interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
+          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7271</v>
+        <v>0.7272999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3578,28 +3894,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>web socket, database, aws cloud services</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AWS CDK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
+          <t>AWS Cloud Development, also called AWS CDK, is the AWS framework that allows the construction of cloud applications.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M01_AU18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.8186</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="5">
@@ -3610,38 +3930,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>kinesis data streams, web socket, core</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>En el cas dels generadors [de Kinesis Data Streams], aquests serien els diferents microserveis de NestJS que tenen la informació sobre els playlogs o les accions en plataforma. En el cas dels playlogs el generador el microservei WebSocket [...] Mentre que l’audit trail té com a generador el Core.</t>
+          <t>AWS CloudFormation is an Amazon service that helps configure AWS resources.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.699</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3652,32 +3972,32 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>kinesis data streams, kinesis data firehose, amazon s3</t>
+          <t>api gateway, core, analytical module</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Per part dels consumidors [de Kinesis Data Streams] tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
+          <t>The communication between the Api Gateway service is through the TCP communication protocol.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8393</v>
+        <v>0.8048999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3688,32 +4008,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>amazon athena, amazon s3</t>
+          <t>core, database service, aws</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
+          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7753</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3724,61 +4044,237 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>aws glue, amazon athena, amazon s3</t>
+          <t>analytical module, aws, database service</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>L’ús d’aquesta [AWS Glue Data Catalog] ha sigut necessària per poder emmagatzemar les metadades de les dades del projecte [...] D’aquesta manera treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
+          <t>The Analytical Module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7289</v>
+        <v>0.7204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>web socket, player, database service, aws</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them. [...] It processes the data coming from the players and stores them in the database and in the cloud services.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.8564000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_38</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>analytical module, amazon athena, amazon s3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The Analytical Module uses the Amazon Athena service to perform queries on data stored in Amazon S3.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7613</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_39</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>aws glue, amazon athena, amazon s3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The AWS Glue service works in conjunction with Athena so that it can read data from S3 correctly.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8133</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_40</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>kinesis data streams, web socket, core</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers (Consumers). [...] In the case of the playlogs the generator is the WebSocket microservice [...] while the audit trail has as generator the Core.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M01_AU22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AU_41</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in the S3.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8238</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Microservices</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema... les diferents capes que formen el sistema es componen de diversos serveis que interactuen entre si.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H14" t="n">
         <v>0.7454</v>
       </c>
     </row>
@@ -3793,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3841,37 +4337,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>The client is the user of the platform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7565</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="3">
@@ -3928,7 +4424,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>customer, server</t>
+          <t>client, server</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3938,260 +4434,116 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.7941</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6775</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Web platform interface</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.7358</v>
+        <v>0.8564000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>Service-oriented</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Database Service</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6101</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M01_AU30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>the presentation layer communicates with the business layer</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.887</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M01_AU28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>This service is responsible for communicating with players.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0.7808</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>0.8186</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.703</v>
+        <v>0.7045</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6415</v>
+        <v>0.7174</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8718</v>
+        <v>0.8462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8529</v>
+        <v>0.9032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8788</v>
+        <v>0.8485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.957</v>
+        <v>0.9626</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7188</v>
+        <v>0.875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9062</v>
+        <v>0.9375</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8764</v>
+        <v>0.8823</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6333</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -559,10 +559,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" t="n">
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -626,16 +624,16 @@
         <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8667</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9286</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="3">
@@ -670,13 +668,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2632</v>
+        <v>0.3333</v>
       </c>
       <c r="F4" t="n">
         <v>0.7143</v>
@@ -725,7 +723,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 19</t>
+          <t>7 / 15</t>
         </is>
       </c>
     </row>
@@ -779,7 +777,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -799,7 +797,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6415</v>
+        <v>0.7174</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +807,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8718</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="12">
@@ -888,19 +886,19 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
         <v>32</v>
@@ -916,7 +914,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
         <v>32</v>
@@ -928,7 +926,7 @@
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
         <v>32</v>
@@ -944,7 +942,7 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>32</v>
@@ -956,7 +954,7 @@
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
         <v>32</v>
@@ -972,7 +970,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
         <v>32</v>
@@ -984,7 +982,7 @@
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
         <v>32</v>
@@ -1000,19 +998,19 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
         <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
         <v>32</v>
@@ -1028,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1165,12 +1163,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1179,67 +1177,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7771</v>
+        <v>0.7532</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS RDS</t>
+          <t>Mobile Platform Interface</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
+          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the mobile platform of Waapiti.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>AWSS RDS</t>
+          <t>Waapiti Mobile Platform</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1247,12 +1245,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1261,67 +1259,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8012</v>
+        <v>0.7771</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mobile Platform</t>
+          <t>AWS RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the Waapiti mobile platform.</t>
+          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>AWSS RDS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU35</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1343,11 +1341,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8139</v>
+        <v>0.8514</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Database Service</t>
+          <t>Relational Database</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1416,7 +1414,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1425,11 +1423,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8436</v>
+        <v>0.8603</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1439,15 +1437,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The communication between the two components is carried out through the internet using the REST API model.</t>
+          <t>For the infrastructure, the cloud services of AWS will be used.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -1457,31 +1459,33 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>41</v>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1489,12 +1493,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1503,39 +1507,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8603</v>
+        <v>0.8605</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>For the infrastructure, the cloud services of AWS will be used.</t>
+          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1545,23 +1553,21 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>44</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1569,12 +1575,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1583,21 +1589,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8605</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1607,19 +1613,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
+          <t>['AU_03', 'P_03']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1629,7 +1635,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1643,7 +1649,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1651,12 +1657,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1665,43 +1671,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9185</v>
+        <v>0.9573</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Web Platform</t>
+          <t>API Player</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the Waapiti mobile platform.</t>
+          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>Api Player</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1711,21 +1717,21 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1733,12 +1739,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1747,11 +1753,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9715</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Web Platform Interface</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1761,29 +1767,29 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The only component that interacts directly with the presentation layer is the Api Gateway module.</t>
+          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the mobile platform of Waapiti.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_03']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>API Gateway Service</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1793,21 +1799,21 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1815,12 +1821,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1829,67 +1835,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9573</v>
+        <v>0.9839</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>API Player</t>
+          <t>DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players by receiving all the information corresponding to it.</t>
+          <t>This service is a non-relational database from AWS.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Api Player</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1897,12 +1903,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1911,67 +1917,67 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9839</v>
+        <v>0.9891</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DynamoDB</t>
+          <t>Analytical Module</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>This service is a non-relational database of AWS.</t>
+          <t>The analytical module has as its main function to obtain and process the data of the playlogs, the connections and the actions in the platform.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1979,81 +1985,85 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9891</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Analytical Module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The analytical module has as its main function to obtain and process the data of the playlogs, the connections and the actions in the platform.</t>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_04']</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>['AU_07']</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>The document labels it as a 'patró de disseny de microserveis' (microservices design pattern), but API Gateway is a well-known design pattern. I have classified it as a Design Pattern.</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2061,17 +2071,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2079,63 +2089,63 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway.</t>
+          <t>The database used is a MySQL database.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['P_02', 'AU_07']</t>
+          <t>['AU_12']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2143,12 +2153,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2161,63 +2171,55 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database.</t>
+          <t>A player consists of a device that can be internal or external, which allows the screens to play content.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['AU_12']</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CF_M01_AU15</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2225,12 +2227,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2243,55 +2245,63 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows the screens to play content.</t>
+          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['AU_09']</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2299,12 +2309,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2317,63 +2327,63 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2381,12 +2391,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2399,17 +2409,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2419,29 +2429,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_07']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2449,13 +2459,13 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2463,90 +2473,94 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
+          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, through the HTTP protocol.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_07']</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>the presentation layer communicates with the business layer more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU24, CF_M01_AU25</t>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>CF_M01_AU25</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2565,28 +2579,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
+          <t>The Api Gateway service processes requests to be able to send them to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_07']</t>
+          <t>['AU_07', 'AU_08', 'AU_09']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway</t>
+          <t>api gateway, core, analytical module</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2597,38 +2611,38 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer more specifically with the Api Gateway</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
+          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway service</t>
+          <t>api gateway service, core service, analytical module</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2647,7 +2661,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The Api Gateway service processes requests to send them to the Core service and the Analytical Module.</t>
+          <t>The Web Socket service carries out the communication between the platform and the players.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2657,18 +2671,18 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_07', 'AU_08', 'AU_09']</t>
+          <t>['AU_11', 'AU_27']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>api gateway, core, analytical module</t>
+          <t>web socket, player</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2679,33 +2693,33 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
+          <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>api gateway service, core service, analytical module</t>
+          <t>player, web socket</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_36</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2729,7 +2743,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The Api Player service is responsible for communicating with the players by receiving all the information corresponding to it. [...] This information is processed and stored.</t>
+          <t>The Api Player service communicates with the players receiving all the information corresponding to it.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2739,13 +2753,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_10', 'AU_30']</t>
+          <t>['AU_10', 'AU_27']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_36</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2787,7 +2801,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2831,7 +2845,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2892,7 +2906,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3033,7 +3047,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3071,13 +3085,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_09']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3279,7 +3293,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3317,13 +3331,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_08']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3437,7 +3451,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3465,7 +3479,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>With the Typescript language.</t>
+          <t>With the language Typescript.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3475,13 +3489,13 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_20']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -3601,7 +3615,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3639,13 +3653,13 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_08']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -3683,7 +3697,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3711,7 +3725,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>The communication between the Api Gateway service is through the TCP communication protocol.</t>
+          <t>The communication between the API Gateway service is through the TCP communication protocol.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3719,11 +3733,15 @@
           <t>44</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>['AU_07']</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -3769,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,7 +3881,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data Lake Service</t>
+          <t>Data Lake</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -3883,85 +3901,85 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AWS CDK</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>core, relational database</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS Cloud Development, also called AWS CDK, is the AWS framework that allows the construction of cloud applications.</t>
+          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7153</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>analytical module, data lake</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS CloudFormation is an Amazon service that helps configure AWS resources.</t>
+          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7708</v>
+        <v>0.7214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3972,32 +3990,28 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>api gateway, core, analytical module</t>
+          <t>web socket, relational database, data lake</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The communication between the Api Gateway service is through the TCP communication protocol.</t>
+          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>API Gateway Service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4008,32 +4022,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>core, database service, aws</t>
+          <t>analytical module, amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>The analytical module uses Amazon Athena to perform queries on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7699</v>
+        <v>0.7788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_35</t>
+          <t>AU_36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4044,26 +4058,26 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>analytical module, aws, database service</t>
+          <t>core, web socket, kinesis data streams</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Analytical Module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>The microservices (Core and Web Socket) send data to the Kinesis Data Stream.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7204</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="9">
@@ -4080,202 +4094,62 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>web socket, player, database service, aws</t>
+          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them. [...] It processes the data coming from the players and stores them in the database and in the cloud services.</t>
+          <t>Kinesis Data Firehose reads from the Kinesis Data Stream and saves the data in Amazon S3.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_38</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>analytical module, amazon athena, amazon s3</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Data lake</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Analytical Module uses the Amazon Athena service to perform queries on data stored in Amazon S3.</t>
+          <t>Un data lake consisteix en un dipòsit de dades que poden ser emmagatzemades en el seu format natural.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.7613</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AU_39</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>aws glue, amazon athena, amazon s3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>The AWS Glue service works in conjunction with Athena so that it can read data from S3 correctly.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.8133</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AU_40</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>kinesis data streams, web socket, core</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers (Consumers). [...] In the case of the playlogs the generator is the WebSocket microservice [...] while the audit trail has as generator the Core.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M01_AU22</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7433999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_41</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in the S3.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M01_AU23</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Kinesis Data Firehose</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8238</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>API Gateway Service</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.7454</v>
+        <v>0.7534</v>
       </c>
     </row>
   </sheetData>
@@ -4434,54 +4308,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.823</v>
+        <v>0.8183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.887</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4492,22 +4366,26 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>player, web socket</t>
+          <t>presentation layer, business layer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="7">
@@ -4534,16 +4412,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Database Service</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7045</v>
+        <v>0.703</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7174</v>
+        <v>0.7692</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8462</v>
+        <v>0.7692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9032</v>
+        <v>0.8182</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8485</v>
+        <v>0.8438</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9626</v>
+        <v>0.9691</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.875</v>
+        <v>0.931</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9375</v>
+        <v>0.931</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8823</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.875</v>
+        <v>0.8966</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6333</v>
+        <v>0.7778</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fixes</t>
+          <t>fixedType</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -624,16 +624,16 @@
         <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.8276</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8929</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="3">
@@ -668,16 +668,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7143</v>
+        <v>0.4286</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 / 15</t>
+          <t>7 / 6</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5 / 5</t>
+          <t>3 / 3</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7174</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="11">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8462</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="12">
@@ -883,25 +883,25 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
         <v>33</v>
       </c>
-      <c r="C2" t="n">
-        <v>31</v>
-      </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -914,22 +914,22 @@
         <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +942,22 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -970,22 +970,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -998,35 +998,35 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fixes</t>
+          <t>fixedType</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>LLM_fixes</t>
+          <t>LLM_fixedType</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>GT_fixes</t>
+          <t>GT_fixedType</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the mobile platform of Waapiti.</t>
+          <t>In the case of this layer, it is formed by the web platform interface and the mobile platform of Waapiti.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7771</v>
+        <v>0.8436</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS RDS</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1273,29 +1273,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
+          <t>The communication between the two components is carried out through the internet using the REST API model.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_03', 'AU_30']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>AWSS RDS</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1305,21 +1305,21 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8514</v>
+        <v>0.8633</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Relational Database</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_04', 'P_04']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1409,12 +1409,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8603</v>
+        <v>0.8889</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Player API Service</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>For the infrastructure, the cloud services of AWS will be used.</t>
+          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>Api Player</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1469,23 +1469,21 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>44</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU13</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1493,12 +1491,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1507,11 +1505,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8605</v>
+        <v>0.9241</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>AWS Cloud Services</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1521,29 +1519,29 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
+          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_04']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1553,21 +1551,23 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>44</v>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9483</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Web Socket Service</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
+          <t>This service is responsible for carrying out the communication between the platform and the players.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1613,19 +1613,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['AU_03', 'P_03']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>API Gateway Service</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1649,7 +1649,7 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1657,12 +1657,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1671,43 +1671,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9573</v>
+        <v>0.9715</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>API Player</t>
+          <t>Web Platform Interface</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players receiving all the information corresponding to it.</t>
+          <t>In the case of this layer, it is formed by the web platform interface and the mobile platform of Waapiti.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_02']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Api Player</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1717,21 +1717,21 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with the players, receiving all the information corresponding to them. The information they can receive can be the status of the player, the contents it plays, the schedules in which these contents should be played, etc. This information is processed and stored</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M01_AU13</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1753,67 +1753,67 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9715</v>
+        <v>0.9839</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Web Platform Interface</t>
+          <t>DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>In the case of this layer, it can be observed that it is formed by the web platform interface and the mobile platform of Waapiti.</t>
+          <t>This service is a non-relational database of AWS.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_02']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1821,12 +1821,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1835,67 +1835,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9839</v>
+        <v>0.9891</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DynamoDB</t>
+          <t>Analytical Module</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS.</t>
+          <t>The analytical module has as its main function to obtain and process the data of the playlogs, the connections and the actions in platform.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1903,81 +1903,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9891</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Analytical Module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The analytical module has as its main function to obtain and process the data of the playlogs, the connections and the actions in the platform.</t>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>The document labels it as a 'patró de disseny de microserveis', but it is a well-known design pattern used to manage service interaction.</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_P04</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1985,17 +1985,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2003,67 +2003,63 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway.</t>
+          <t>The database used is a MySQL database.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_07']</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>The document labels it as a 'patró de disseny de microserveis' (microservices design pattern), but API Gateway is a well-known design pattern. I have classified it as a Design Pattern.</t>
-        </is>
-      </c>
+          <t>['AU_12']</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M01_P04</t>
+          <t>CF_M01_AU32</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2071,12 +2067,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2089,7 +2085,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2099,29 +2095,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database.</t>
+          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_12']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2131,21 +2127,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
+          <t>CF_M01_AU20</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2153,12 +2149,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2171,55 +2167,63 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows the screens to play content.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>['P_02']</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CF_M01_P02</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2227,12 +2231,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2245,63 +2249,63 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The Amazon Athena service is a service that allows SQL queries to be performed on data stored in Amazon S3.</t>
+          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['AU_03', 'P_04']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Service that allows you to perform SQL queries on data stored in Amazon S3</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M01_AU20</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2309,12 +2313,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2327,17 +2331,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2347,29 +2351,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_03', 'AU_30']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user. In this project, it is the visual interface of the Waapiti platform.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -2377,13 +2381,13 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2391,94 +2395,94 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
+          <t>La capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_07']</t>
+          <t>['AU_02', 'AU_07']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>the presentation layer communicates with the business layer more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M01_AU24, CF_M01_AU25</t>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>CF_M01_AU25</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2497,28 +2501,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, through the HTTP protocol.</t>
+          <t>La comunicació entre el servei de l’Api Gateway és mitjançant el protocol de comunicació TCP.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_02', 'AU_07']</t>
+          <t>['AU_07', 'AU_08', 'AU_09']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway</t>
+          <t>api gateway service, core service, analytical module</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2529,139 +2533,143 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer more specifically with the Api Gateway</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
+          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway service</t>
+          <t>api gateway service, core service, analytical module</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The Api Gateway service processes requests to be able to send them to the Core service and the analytical module.</t>
+          <t>As a framework, NestJS will be used.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_07', 'AU_08', 'AU_09']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>api gateway, core, analytical module</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>api gateway service, core service, analytical module</t>
-        </is>
-      </c>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>API Gateway Service</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The Web Socket service carries out the communication between the platform and the players.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2671,29 +2679,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_11', 'AU_27']</t>
+          <t>['AU_03', 'P_03']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>web socket, player</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>API Gateway Service</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2701,112 +2709,108 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M01_AU27, CF_M01_AU14</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>CF_M01_AU10</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>The Api Player service communicates with the players receiving all the information corresponding to it.</t>
+          <t>This is the object storage service of AWS.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_10', 'AU_27']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>api player, player</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating with players.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M01_AU27, CF_M01_AU13</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2819,7 +2823,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2829,29 +2833,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>As a framework, NestJS will be used.</t>
+          <t>The AWS Glue service is a serverless data integration service.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2861,21 +2865,21 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>This framework is a NodeJS framework whose main function is to create backend applications. In this project, this framework has been used to develop the different services that interact with each other.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2883,12 +2887,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2901,63 +2905,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU06</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2965,17 +2969,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2983,63 +2987,63 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>This is the object storage service of AWS.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3047,12 +3051,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3065,7 +3069,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3075,29 +3079,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The AWS Glue service is a serverless data integration service.</t>
+          <t>Kinesis Data Streams is a data processing and ingestion service aimed especially at data streaming.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['AU_13']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3107,11 +3111,13 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>49</v>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>50, 51</t>
+        </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3121,7 +3127,7 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3129,17 +3135,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3147,17 +3153,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>This layer is the core of the application and is responsible for processing all the information.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3165,45 +3171,37 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['P_02']</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>This layer is the core of the application, which is responsible for processing all the information. In our context, it is the software that is responsible for processing user requests.</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="P26" t="n">
         <v>41</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>CF_M01_P02</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M01_AU06</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3211,17 +3209,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3229,63 +3227,63 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
+          <t>With the language Typescript.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
+          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
-          <t>CF_M01_P02</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3293,12 +3291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3311,65 +3309,63 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams is a data processing and ingestion service specifically aimed at data streaming.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['AU_08']</t>
+          <t>['P_02']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>50, 51</t>
-        </is>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>41</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P02</t>
         </is>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3377,17 +3373,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3395,55 +3391,63 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>['AU_13']</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3451,12 +3455,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3469,7 +3473,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3479,29 +3483,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>With the language Typescript.</t>
+          <t>The communication between the API Gateway service is through the TCP communication protocol.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['AU_20']</t>
+          <t>['AU_03', 'AU_31']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3511,7 +3515,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -3519,262 +3523,16 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU26,CF_M01_AU27</t>
         </is>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU31</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>['P_02']</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>CF_M01_P02</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>CF_M01_AU23</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Kinesis Data Firehose</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>The Kinesis Data Firehose service has as its main function the loading of large amounts of data into data warehouses.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['AU_08']</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Kinesis Data Firehose</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>CF_M01_AU23</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>The communication between the API Gateway service is through the TCP communication protocol.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>['AU_07']</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>CF_M01_AU26,CF_M01_AU27</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>CF_M01_AU31</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3787,7 +3545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3871,147 +3629,151 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data Lake</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
+          <t>For the infrastructure, the cloud services of AWS will be used.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7526</v>
+        <v>0.8603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>core, relational database</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This database is implemented in the RDS service.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7699</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>analytical module, data lake</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AWS CDK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>The AWS CDK is the AWS framework that allows the construction of applications in the cloud.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7214</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>web socket, relational database, data lake</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
+          <t>AWS CloudFormation is an Amazon service that helps configure AWS resources.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0.799</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_35</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4022,32 +3784,28 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>analytical module, amazon athena, amazon s3</t>
+          <t>web socket service, player api service</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The analytical module uses Amazon Athena to perform queries on data stored in Amazon S3.</t>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.7788</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_36</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4058,98 +3816,58 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>core, web socket, kinesis data streams</t>
+          <t>web socket service, database, aws cloud services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The microservices (Core and Web Socket) send data to the Kinesis Data Stream.</t>
+          <t>Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.7889</v>
+        <v>0.7296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_37</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose reads from the Kinesis Data Stream and saves the data in Amazon S3.</t>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8948</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Data lake</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Un data lake consisteix en un dipòsit de dades que poden ser emmagatzemades en el seu format natural.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7534</v>
+        <v>0.7454</v>
       </c>
     </row>
   </sheetData>
@@ -4163,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4211,43 +3929,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU01</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>User</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8333</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4257,13 +3975,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for processing user requests.</t>
+          <t>The client is the user of the platform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4277,62 +3995,62 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8237</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>client, server</t>
-        </is>
-      </c>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.8183</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>client, server</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -4340,7 +4058,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4349,7 +4067,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="6">
@@ -4391,37 +4109,137 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CF_M01_AU28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>This service is responsible for communicating with players.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.8078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>This service is responsible for communicating between the platform and the players.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.847</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M01_AU35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AWSS RDS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.742</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.703</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Core Service</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.766</v>
       </c>
     </row>
   </sheetData>
